--- a/data/flow.xlsx
+++ b/data/flow.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johnn\PycharmProjects\PythonProject\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johnn\PycharmProjects\CallScheduleCreator\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DEF15B-89E9-4FEC-9177-5DD1A9F038C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E883C65F-0143-4C53-B005-EDE665002D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42570" yWindow="0" windowWidth="15135" windowHeight="15585" xr2:uid="{AE87C787-1FF4-422C-AE20-6CC5E96521CE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{AE87C787-1FF4-422C-AE20-6CC5E96521CE}"/>
   </bookViews>
   <sheets>
     <sheet name="master_block_calendar" sheetId="1" r:id="rId1"/>
@@ -203,48 +203,6 @@
     <t>AMB/ELE</t>
   </si>
   <si>
-    <t>PGY2-1</t>
-  </si>
-  <si>
-    <t>PGY2-2</t>
-  </si>
-  <si>
-    <t>PGY2-3</t>
-  </si>
-  <si>
-    <t>PGY2-4</t>
-  </si>
-  <si>
-    <t>PGY2-5</t>
-  </si>
-  <si>
-    <t>PGY2-6</t>
-  </si>
-  <si>
-    <t>PGY2-7</t>
-  </si>
-  <si>
-    <t>PGY2-8</t>
-  </si>
-  <si>
-    <t>PGY3-1</t>
-  </si>
-  <si>
-    <t>PGY3-2</t>
-  </si>
-  <si>
-    <t>PGY3-3</t>
-  </si>
-  <si>
-    <t>PGY3-4</t>
-  </si>
-  <si>
-    <t>PGY3-5</t>
-  </si>
-  <si>
-    <t>PGY3-6</t>
-  </si>
-  <si>
     <t>PGY1-1</t>
   </si>
   <si>
@@ -360,6 +318,48 @@
   </si>
   <si>
     <t>PEDI/PEDO</t>
+  </si>
+  <si>
+    <t>Riaz</t>
+  </si>
+  <si>
+    <t>Behaj</t>
+  </si>
+  <si>
+    <t>Clark</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>Coggeshall</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Wallace</t>
+  </si>
+  <si>
+    <t>Schaeffer</t>
+  </si>
+  <si>
+    <t>Prahbu</t>
+  </si>
+  <si>
+    <t>Davis</t>
+  </si>
+  <si>
+    <t>Snell</t>
+  </si>
+  <si>
+    <t>Fuentes</t>
+  </si>
+  <si>
+    <t>Hall</t>
+  </si>
+  <si>
+    <t>McMurray</t>
   </si>
 </sst>
 </file>
@@ -885,24 +885,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.453125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.453125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="17" max="17" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7265625" customWidth="1"/>
+    <col min="17" max="17" width="36.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -944,59 +944,59 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="H2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>87</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>101</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
@@ -1032,9 +1032,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -1043,7 +1043,7 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
@@ -1076,15 +1076,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -1120,9 +1120,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
@@ -1161,12 +1161,12 @@
         <v>14</v>
       </c>
       <c r="N6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
@@ -1196,7 +1196,7 @@
         <v>16</v>
       </c>
       <c r="K7" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="L7" t="s">
         <v>14</v>
@@ -1208,12 +1208,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
@@ -1252,9 +1252,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
@@ -1281,7 +1281,7 @@
         <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="K9" t="s">
         <v>14</v>
@@ -1296,9 +1296,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1334,15 +1334,15 @@
         <v>15</v>
       </c>
       <c r="M10" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="N10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
         <v>35</v>
@@ -1363,7 +1363,7 @@
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s">
         <v>28</v>
@@ -1384,9 +1384,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
@@ -1395,7 +1395,7 @@
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
         <v>31</v>
@@ -1428,9 +1428,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
@@ -1472,9 +1472,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
@@ -1510,62 +1510,62 @@
         <v>17</v>
       </c>
       <c r="M14" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="N14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="M15" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" t="s">
         <v>92</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" t="s">
-        <v>106</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -1598,15 +1598,15 @@
         <v>14</v>
       </c>
       <c r="M16" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="N16" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="B17" t="s">
         <v>44</v>
@@ -1627,7 +1627,7 @@
         <v>43</v>
       </c>
       <c r="H17" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s">
         <v>42</v>
@@ -1645,12 +1645,12 @@
         <v>45</v>
       </c>
       <c r="N17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="B18" t="s">
         <v>40</v>
@@ -1659,7 +1659,7 @@
         <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s">
         <v>39</v>
@@ -1689,12 +1689,12 @@
         <v>14</v>
       </c>
       <c r="N18" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="B19" t="s">
         <v>42</v>
@@ -1709,7 +1709,7 @@
         <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="G19" t="s">
         <v>14</v>
@@ -1730,21 +1730,21 @@
         <v>44</v>
       </c>
       <c r="M19" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="N19" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
         <v>39</v>
@@ -1765,10 +1765,10 @@
         <v>44</v>
       </c>
       <c r="J20" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K20" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="L20" t="s">
         <v>41</v>
@@ -1780,9 +1780,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s">
         <v>44</v>
@@ -1794,7 +1794,7 @@
         <v>42</v>
       </c>
       <c r="E21" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="F21" t="s">
         <v>40</v>
@@ -1806,7 +1806,7 @@
         <v>15</v>
       </c>
       <c r="I21" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J21" t="s">
         <v>43</v>
@@ -1824,9 +1824,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="B22" t="s">
         <v>39</v>
@@ -1853,13 +1853,13 @@
         <v>15</v>
       </c>
       <c r="J22" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="L22" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="M22" t="s">
         <v>14</v>
@@ -1868,9 +1868,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
@@ -1894,13 +1894,13 @@
         <v>40</v>
       </c>
       <c r="I23" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="J23" t="s">
         <v>44</v>
       </c>
       <c r="K23" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="L23" t="s">
         <v>44</v>
@@ -1912,59 +1912,59 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="N24" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
       </c>
       <c r="D25" t="s">
         <v>48</v>
@@ -1991,7 +1991,7 @@
         <v>50</v>
       </c>
       <c r="L25" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="M25" t="s">
         <v>44</v>
@@ -2000,9 +2000,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
         <v>41</v>
@@ -2017,7 +2017,7 @@
         <v>50</v>
       </c>
       <c r="F26" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="G26" t="s">
         <v>49</v>
@@ -2032,7 +2032,7 @@
         <v>14</v>
       </c>
       <c r="K26" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="L26" t="s">
         <v>44</v>
@@ -2044,9 +2044,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="B27" t="s">
         <v>47</v>
@@ -2064,10 +2064,10 @@
         <v>44</v>
       </c>
       <c r="G27" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="I27" t="s">
         <v>44</v>
@@ -2076,7 +2076,7 @@
         <v>14</v>
       </c>
       <c r="K27" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="L27" t="s">
         <v>53</v>
@@ -2088,9 +2088,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -2102,10 +2102,10 @@
         <v>52</v>
       </c>
       <c r="E28" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="F28" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s">
         <v>44</v>
@@ -2132,12 +2132,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
         <v>44</v>
@@ -2164,7 +2164,7 @@
         <v>48</v>
       </c>
       <c r="K29" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="L29" t="s">
         <v>50</v>
@@ -2176,12 +2176,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -2199,7 +2199,7 @@
         <v>50</v>
       </c>
       <c r="H30" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="I30" t="s">
         <v>44</v>
@@ -2208,7 +2208,7 @@
         <v>41</v>
       </c>
       <c r="K30" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="L30" t="s">
         <v>44</v>
